--- a/outputs/91-34.xlsx
+++ b/outputs/91-34.xlsx
@@ -282,16 +282,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -526,806 +530,806 @@
   <dimension ref="B1:O39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="26.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="7.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="26.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>37357</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>35994</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>30539</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="E6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>24613</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="0" t="s">
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>24613</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="0" t="s">
+      <c r="G7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>37266</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="0" t="s">
+      <c r="G8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>37266</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="0" t="s">
+      <c r="G9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>31140</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="0" t="s">
+      <c r="G10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2" t="n">
+      <c r="E11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>31140</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="0" t="s">
+      <c r="G11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="2" t="n">
+      <c r="E12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>37717</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="0" t="s">
+      <c r="G12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>36239</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="0" t="s">
+      <c r="G13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>25068</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="0" t="s">
+      <c r="G14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="2" t="n">
+      <c r="E15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>25709</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="0" t="s">
+      <c r="G15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>25068</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="0" t="s">
+      <c r="G16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="2" t="n">
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>25709</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="0" t="s">
+      <c r="G17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="2" t="n">
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>34143</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="0" t="s">
+      <c r="G18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="2" t="n">
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>34143</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="0" t="s">
+      <c r="G19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="2" t="n">
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>35061</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="0" t="s">
+      <c r="G20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="2" t="n">
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>35061</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="0" t="s">
+      <c r="G21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="3" t="n">
         <v>29892</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="0" t="s">
+      <c r="G22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>29892</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="0" t="s">
+      <c r="G23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="2" t="n">
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="3" t="n">
         <v>37763</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="0" t="s">
+      <c r="G24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="2" t="n">
+      <c r="E25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>37763</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="0" t="s">
+      <c r="G25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="2" t="n">
+      <c r="E26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>36008</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="0" t="s">
+      <c r="G26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="2" t="n">
+      <c r="E27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>36008</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="0" t="s">
+      <c r="G27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E28" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="2" t="n">
+      <c r="E28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>35082</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="0" t="s">
+      <c r="G28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="2" t="n">
+      <c r="E29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>35082</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="0" t="s">
+      <c r="G29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="2" t="n">
+      <c r="E30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="3" t="n">
         <v>36367</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="0" t="s">
+      <c r="G30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="2" t="n">
+      <c r="E31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>36367</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="0" t="s">
+      <c r="G31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="3" t="n">
         <v>38916</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="0" t="s">
+      <c r="G32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E33" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="2" t="n">
+      <c r="E33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>32031</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H33" s="0" t="s">
+      <c r="G33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="3" t="n">
         <v>31934</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="0" t="s">
+      <c r="G34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" s="2" t="n">
+      <c r="E35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>32031</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="0" t="s">
+      <c r="G35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="3" t="n">
         <v>31934</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="0" t="s">
+      <c r="G36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" s="2" t="n">
+      <c r="E37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>38709</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="0" t="s">
+      <c r="G37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="2" t="n">
+      <c r="E38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>38709</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="0" t="s">
+      <c r="G38" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="3" t="n">
         <v>37051</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="0" t="s">
+      <c r="G39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/outputs/91-34.xlsx
+++ b/outputs/91-34.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="61">
   <si>
     <t xml:space="preserve">SSN</t>
   </si>
@@ -142,9 +142,6 @@
     <t xml:space="preserve">Casey</t>
   </si>
   <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
     <t xml:space="preserve">Computer</t>
   </si>
   <si>
@@ -190,10 +187,10 @@
     <t xml:space="preserve">Jones</t>
   </si>
   <si>
+    <t xml:space="preserve">Seamus</t>
+  </si>
+  <si>
     <t xml:space="preserve">Christina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seamus</t>
   </si>
   <si>
     <t xml:space="preserve">Plam</t>
@@ -527,7 +524,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:O39"/>
+  <dimension ref="B1:O31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.71"/>
@@ -670,27 +667,27 @@
         <v>26</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>24613</v>
+        <v>37266</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -710,67 +707,67 @@
         <v>26</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>37266</v>
+        <v>31140</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>31140</v>
+        <v>37717</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>31140</v>
+        <v>36239</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -778,13 +775,13 @@
         <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>37717</v>
+        <v>36239</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>26</v>
@@ -798,19 +795,19 @@
         <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>36239</v>
+        <v>25068</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -818,13 +815,13 @@
         <v>33</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>25068</v>
+        <v>25709</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>26</v>
@@ -838,73 +835,73 @@
         <v>33</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>25709</v>
+        <v>25068</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>25068</v>
+        <v>34143</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25709</v>
+        <v>35061</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>34143</v>
+        <v>35061</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>26</v>
@@ -915,36 +912,36 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>34143</v>
+        <v>29892</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>35061</v>
+        <v>37763</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>26</v>
@@ -955,16 +952,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>35061</v>
+        <v>37763</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>26</v>
@@ -975,56 +972,56 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>29892</v>
+        <v>36008</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>29892</v>
+        <v>35082</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>37763</v>
+        <v>36367</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>26</v>
@@ -1035,16 +1032,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>37763</v>
+        <v>36367</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>26</v>
@@ -1055,16 +1052,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>36008</v>
+        <v>38916</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>26</v>
@@ -1075,16 +1072,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>36008</v>
+        <v>31934</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>26</v>
@@ -1095,241 +1092,81 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>35082</v>
+        <v>32031</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>35082</v>
+        <v>38709</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>36367</v>
+        <v>38709</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>36367</v>
+        <v>37051</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>26</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>38916</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>32031</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>31934</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>32031</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>31934</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>38709</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>38709</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>37051</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="1" t="s">
         <v>30</v>
       </c>
     </row>
